--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -483,38 +483,38 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>562774.5800000001</v>
+        <v>738069.76</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228669.74</v>
+        <v>312448.74</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1141093</v>
+        <v>1188457</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-50.7%</t>
+          <t>-37.9%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>334104.8400000001</v>
+        <v>425621.02</v>
       </c>
       <c r="J2" t="n">
-        <v>773841</v>
+        <v>755375</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-56.8%</t>
+          <t>-43.7%</t>
         </is>
       </c>
     </row>
@@ -528,38 +528,38 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>270721</v>
+        <v>317341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>60174</v>
+        <v>53574</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>271283</v>
+        <v>295883</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>+7.3%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>210547</v>
+        <v>263767</v>
       </c>
       <c r="J3" t="n">
-        <v>78303</v>
+        <v>89252</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>+168.9%</t>
+          <t>+195.5%</t>
         </is>
       </c>
     </row>
@@ -573,38 +573,38 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>1739108.44</v>
+        <v>1905323.74</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>207627</v>
+        <v>224655</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1479698.82</v>
+        <v>1655887.67</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>+17.5%</t>
+          <t>+15.1%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1531481.44</v>
+        <v>1680668.74</v>
       </c>
       <c r="J4" t="n">
-        <v>1164525.41</v>
+        <v>1217947.26</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+31.5%</t>
+          <t>+38.0%</t>
         </is>
       </c>
     </row>
@@ -618,38 +618,38 @@
         <v>14410000</v>
       </c>
       <c r="C5" t="n">
-        <v>2572604.02</v>
+        <v>2960734.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>496470.74</v>
+        <v>590677.7400000001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2892074.82</v>
+        <v>3140227.67</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2076133.28</v>
+        <v>2370056.76</v>
       </c>
       <c r="J5" t="n">
-        <v>2016669.41</v>
+        <v>2062574.26</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>+14.9%</t>
         </is>
       </c>
     </row>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -483,38 +483,38 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>738069.76</v>
+        <v>792768.76</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>312448.74</v>
+        <v>353558.64</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1188457</v>
+        <v>1238463</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>425621.02</v>
+        <v>439210.12</v>
       </c>
       <c r="J2" t="n">
-        <v>755375</v>
+        <v>803587</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-43.7%</t>
+          <t>-45.3%</t>
         </is>
       </c>
     </row>
@@ -528,11 +528,11 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>317341</v>
+        <v>366721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -540,7 +540,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -548,18 +548,18 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>+7.3%</t>
+          <t>+23.9%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>263767</v>
+        <v>313147</v>
       </c>
       <c r="J3" t="n">
         <v>89252</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>+195.5%</t>
+          <t>+250.9%</t>
         </is>
       </c>
     </row>
@@ -573,15 +573,15 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>1905323.74</v>
+        <v>2130849.22</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224655</v>
+        <v>251835</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -589,22 +589,22 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1655887.67</v>
+        <v>1889501.67</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>+15.1%</t>
+          <t>+12.8%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1680668.74</v>
+        <v>1879014.22</v>
       </c>
       <c r="J4" t="n">
-        <v>1217947.26</v>
+        <v>1450061.26</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+38.0%</t>
+          <t>+29.6%</t>
         </is>
       </c>
     </row>
@@ -618,15 +618,15 @@
         <v>14410000</v>
       </c>
       <c r="C5" t="n">
-        <v>2960734.5</v>
+        <v>3290338.98</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>590677.7400000001</v>
+        <v>658967.6400000001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3140227.67</v>
+        <v>3423847.67</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2370056.76</v>
+        <v>2631371.34</v>
       </c>
       <c r="J5" t="n">
-        <v>2062574.26</v>
+        <v>2342900.26</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+14.9%</t>
+          <t>+12.3%</t>
         </is>
       </c>
     </row>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,19 +483,19 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>792768.76</v>
+        <v>1020612.45</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353558.64</v>
+        <v>369278.64</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>439210.12</v>
+        <v>651333.8100000001</v>
       </c>
       <c r="J2" t="n">
         <v>803587</v>
@@ -528,11 +528,11 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>366721</v>
+        <v>419321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -540,7 +540,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>313147</v>
+        <v>365747</v>
       </c>
       <c r="J3" t="n">
         <v>89252</v>
@@ -573,19 +573,19 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>2130849.22</v>
+        <v>2417284.96</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>251835</v>
+        <v>310995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1879014.22</v>
+        <v>2106289.96</v>
       </c>
       <c r="J4" t="n">
         <v>1450061.26</v>
@@ -605,51 +605,6 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>+29.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>南区合计</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>14410000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3290338.98</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>22.8%</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>658967.6400000001</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>3423847.67</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-3.9%</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2631371.34</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2342900.26</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>+12.3%</t>
         </is>
       </c>
     </row>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,27 +449,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>上月完成</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>完成环比</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
           <t>本月净流水</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>上月净流水</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>净流水环比</t>
         </is>
       </c>
     </row>
@@ -487,7 +467,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -499,23 +479,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1238463</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-36.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>651333.8100000001</v>
-      </c>
-      <c r="J2" t="n">
-        <v>803587</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-45.3%</t>
-        </is>
+        <v>651333.8099999999</v>
       </c>
     </row>
     <row r="3">
@@ -532,7 +496,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -544,23 +508,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>295883</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>+23.9%</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
         <v>365747</v>
-      </c>
-      <c r="J3" t="n">
-        <v>89252</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>+250.9%</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -577,7 +525,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -589,23 +537,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1889501.67</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>+12.8%</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
         <v>2106289.96</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1450061.26</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>+29.6%</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>1020612.45</v>
+        <v>1172725.65</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>369278.64</v>
+        <v>452090.64</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>651333.8099999999</v>
+        <v>720635.01</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>419321</v>
+        <v>437731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53574</v>
+        <v>83374</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>365747</v>
+        <v>354357</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>2417284.96</v>
+        <v>2603268.59</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>310995</v>
+        <v>341724</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2106289.96</v>
+        <v>2261544.59</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -521,19 +521,19 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>2603268.59</v>
+        <v>2610268.59</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>341724</v>
+        <v>348724</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>1172725.65</v>
+        <v>1253054.65</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>452090.64</v>
+        <v>497729.64</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>720635.01</v>
+        <v>755325.01</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>437731</v>
+        <v>565827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>83374</v>
+        <v>136924</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>354357</v>
+        <v>428903</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>2610268.59</v>
+        <v>2762417.59</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>348724</v>
+        <v>428652</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2261544.59</v>
+        <v>2333765.59</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>1253054.65</v>
+        <v>1292222.65</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>497729.64</v>
+        <v>498905.54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>755325.01</v>
+        <v>793317.1099999999</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>565827</v>
+        <v>575827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>428903</v>
+        <v>438903</v>
       </c>
     </row>
     <row r="4">
@@ -521,11 +521,11 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>2762417.59</v>
+        <v>3012506.34</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -533,11 +533,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2333765.59</v>
+        <v>2583854.34</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,7 +463,7 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>1292222.65</v>
+        <v>1292251.65</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>793317.1099999999</v>
+        <v>793346.1099999999</v>
       </c>
     </row>
     <row r="3">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>1292251.65</v>
+        <v>1681385.62</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>498905.54</v>
+        <v>542520.54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>793346.1099999999</v>
+        <v>1138865.08</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>575827</v>
+        <v>612146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>136924</v>
+        <v>140924</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>438903</v>
+        <v>471222</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>3012506.34</v>
+        <v>3565300.36</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>428652</v>
+        <v>434452</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2583854.34</v>
+        <v>3130848.36</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>1681385.62</v>
+        <v>1422328.61</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>542520.54</v>
+        <v>504636.54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1138865.08</v>
+        <v>917692.0700000001</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>612146</v>
+        <v>587346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>140924</v>
+        <v>136924</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>471222</v>
+        <v>450422</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>3565300.36</v>
+        <v>3498303.16</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>434452</v>
+        <v>429452</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3130848.36</v>
+        <v>3068851.16</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>1422328.61</v>
+        <v>1681385.62</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>504636.54</v>
+        <v>542520.54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>917692.0700000001</v>
+        <v>1138865.08</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>587346</v>
+        <v>612146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>136924</v>
+        <v>140924</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>450422</v>
+        <v>471222</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>3498303.16</v>
+        <v>3565300.36</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>429452</v>
+        <v>434452</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3068851.16</v>
+        <v>3130848.36</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -521,11 +521,11 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>3565300.36</v>
+        <v>3447930.36</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -533,11 +533,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3130848.36</v>
+        <v>3013478.36</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>1681385.62</v>
+        <v>1768303.42</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>542520.54</v>
+        <v>557092.54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1138865.08</v>
+        <v>1211210.88</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>612146</v>
+        <v>669666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>140924</v>
+        <v>146924</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>471222</v>
+        <v>522742</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>3447930.36</v>
+        <v>4520196.46</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>434452</v>
+        <v>436652</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3013478.36</v>
+        <v>4083544.46</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -521,11 +521,11 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>4520196.46</v>
+        <v>3543746.66</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -533,11 +533,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4083544.46</v>
+        <v>3107094.66</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,15 +463,15 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>1768303.42</v>
+        <v>1795248.42</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>557092.54</v>
+        <v>564930.54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1211210.88</v>
+        <v>1230317.88</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>669666</v>
+        <v>680573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>522742</v>
+        <v>533649</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>3543746.66</v>
+        <v>3735666.86</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>436652</v>
+        <v>440700</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3107094.66</v>
+        <v>3294966.859999999</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>1795248.42</v>
+        <v>1936124.33</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>564930.54</v>
+        <v>575085.54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1230317.88</v>
+        <v>1361038.79</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>680573</v>
+        <v>670632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>146924</v>
+        <v>160124</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>533649</v>
+        <v>510508</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>3735666.86</v>
+        <v>3900529.35</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>440700</v>
+        <v>554234</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3294966.859999999</v>
+        <v>3346295.35</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -521,11 +521,11 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>3900529.35</v>
+        <v>3922293.659999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -533,11 +533,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3346295.35</v>
+        <v>3368059.659999999</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,15 +463,15 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>1936124.33</v>
+        <v>2197346.08</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>575085.54</v>
+        <v>652236.4500000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1361038.79</v>
+        <v>1545109.63</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>670632</v>
+        <v>738629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>160124</v>
+        <v>170124</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>510508</v>
+        <v>568505</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>3922293.659999999</v>
+        <v>4900991.86</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>554234</v>
+        <v>583197.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3368059.659999999</v>
+        <v>4317794.380000001</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>2197346.08</v>
+        <v>2407435.08</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>652236.4500000001</v>
+        <v>776494.7799999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1545109.63</v>
+        <v>1630940.3</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>738629</v>
+        <v>788848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>170124</v>
+        <v>190872</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>568505</v>
+        <v>597976</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>4900991.86</v>
+        <v>5172488.44</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>583197.48</v>
+        <v>627427.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4317794.380000001</v>
+        <v>4545060.96</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>2407435.08</v>
+        <v>2501617.42</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>776494.7799999999</v>
+        <v>802773.7799999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1630940.3</v>
+        <v>1698843.64</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>788848</v>
+        <v>811497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>190872</v>
+        <v>216270</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>597976</v>
+        <v>595227</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>5172488.44</v>
+        <v>5358259.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>627427.48</v>
+        <v>641427.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4545060.96</v>
+        <v>4716832.22</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>2501617.42</v>
+        <v>2607737.63</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>802773.7799999999</v>
+        <v>840545.7799999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1698843.64</v>
+        <v>1767191.85</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>811497</v>
+        <v>880213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>216270</v>
+        <v>219270</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>595227</v>
+        <v>660943</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>5358259.7</v>
+        <v>5557199.18</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>641427.48</v>
+        <v>711027.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4716832.22</v>
+        <v>4846171.699999999</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>2607737.63</v>
+        <v>2772829.68</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>840545.7799999999</v>
+        <v>886211.7799999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1767191.85</v>
+        <v>1886617.9</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>880213</v>
+        <v>923993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219270</v>
+        <v>236268</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>660943</v>
+        <v>687725</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>5557199.18</v>
+        <v>5767289.78</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>711027.48</v>
+        <v>712046.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4846171.699999999</v>
+        <v>5055243.3</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>2772829.68</v>
+        <v>2824554.93</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>886211.7799999999</v>
+        <v>900112.7799999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1886617.9</v>
+        <v>1924442.15</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>923993</v>
+        <v>932613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>236268</v>
+        <v>287768</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>687725</v>
+        <v>644845</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>5767289.78</v>
+        <v>5952182.34</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>712046.48</v>
+        <v>744103.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5055243.3</v>
+        <v>5208078.86</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -521,7 +521,7 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>5952182.34</v>
+        <v>5958478.69</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -529,15 +529,15 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>744103.48</v>
+        <v>760603.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5208078.86</v>
+        <v>5197875.210000001</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>2824554.93</v>
+        <v>2877722.25</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>900112.7799999999</v>
+        <v>901232.7799999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1924442.15</v>
+        <v>1976489.47</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>932613</v>
+        <v>944942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>287768</v>
+        <v>287797</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>644845</v>
+        <v>657145</v>
       </c>
     </row>
     <row r="4">
@@ -521,11 +521,11 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>5958478.69</v>
+        <v>6396818.92</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -533,11 +533,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5197875.210000001</v>
+        <v>5636215.44</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>2877722.25</v>
+        <v>2930269.24</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>901232.7799999999</v>
+        <v>902828.7799999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1976489.47</v>
+        <v>2027440.46</v>
       </c>
     </row>
     <row r="3">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>6396818.92</v>
+        <v>6841398.959999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760603.48</v>
+        <v>760641.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5636215.44</v>
+        <v>6080757.48</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4450000</v>
       </c>
       <c r="C2" t="n">
-        <v>2930269.24</v>
+        <v>3296859.23</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>902828.7799999999</v>
+        <v>917592.9799999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2027440.46</v>
+        <v>2379266.25</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1700000</v>
       </c>
       <c r="C3" t="n">
-        <v>944942</v>
+        <v>1319532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>287797</v>
+        <v>354185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>657145</v>
+        <v>965347</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8260000</v>
       </c>
       <c r="C4" t="n">
-        <v>6841398.959999999</v>
+        <v>7495326.549999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760641.48</v>
+        <v>858108.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6080757.48</v>
+        <v>6637218.07</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -460,26 +460,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4450000</v>
+        <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>3296859.23</v>
+        <v>293542.62</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>917592.9799999999</v>
+        <v>140948</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2379266.25</v>
+        <v>152594.62</v>
       </c>
     </row>
     <row r="3">
@@ -489,26 +489,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1700000</v>
+        <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>1319532</v>
+        <v>112716.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>354185</v>
+        <v>73800</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>965347</v>
+        <v>38916.36</v>
       </c>
     </row>
     <row r="4">
@@ -518,26 +518,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8260000</v>
+        <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>7495326.549999999</v>
+        <v>599362.0699999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>858108.48</v>
+        <v>31094</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6637218.07</v>
+        <v>568268.0699999999</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -460,14 +460,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3640000</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>293542.62</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -489,14 +489,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1120000</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>112716.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -460,14 +460,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>3640000</v>
       </c>
       <c r="C2" t="n">
         <v>293542.62</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -489,14 +489,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1120000</v>
       </c>
       <c r="C3" t="n">
         <v>112716.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>293542.62</v>
+        <v>520415.55</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>140948</v>
+        <v>231737</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>152594.62</v>
+        <v>288678.55</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>112716.36</v>
+        <v>282723.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73800</v>
+        <v>129600</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>38916.36</v>
+        <v>153123.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>599362.0699999999</v>
+        <v>1465251.93</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>31094</v>
+        <v>70528.98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>568268.0699999999</v>
+        <v>1394722.95</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>520415.55</v>
+        <v>793874.9500000001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>231737</v>
+        <v>295064</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>288678.55</v>
+        <v>498810.95</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>282723.36</v>
+        <v>367911.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>129600</v>
+        <v>130600</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>153123.36</v>
+        <v>237311.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>1465251.93</v>
+        <v>1655709.35</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70528.98</v>
+        <v>117714.65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1394722.95</v>
+        <v>1537994.7</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>793874.9500000001</v>
+        <v>991192.95</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>295064</v>
+        <v>313996.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>498810.95</v>
+        <v>677196.15</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>367911.36</v>
+        <v>391691.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>130600</v>
+        <v>137200</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>237311.36</v>
+        <v>254491.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>1655709.35</v>
+        <v>1846178.83</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>117714.65</v>
+        <v>159251.65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1537994.7</v>
+        <v>1686927.18</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>991192.95</v>
+        <v>1113044.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>313996.8</v>
+        <v>346206.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>677196.15</v>
+        <v>766837.4</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>391691.36</v>
+        <v>435931.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>254491.36</v>
+        <v>298731.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>1846178.83</v>
+        <v>2097548.85</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>159251.65</v>
+        <v>176089.65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1686927.18</v>
+        <v>1921459.2</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>1113044.2</v>
+        <v>1283074.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>346206.8</v>
+        <v>410168.96</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>766837.4</v>
+        <v>872905.2399999999</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>435931.36</v>
+        <v>467449.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>137200</v>
+        <v>139000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>298731.36</v>
+        <v>328449.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>2097548.85</v>
+        <v>2243190.59</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>176089.65</v>
+        <v>200727.65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1921459.2</v>
+        <v>2042462.94</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -521,7 +521,7 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>2243190.59</v>
+        <v>2243289.59</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -529,11 +529,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>200727.65</v>
+        <v>200826.65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
